--- a/RSVP_admin/assets/guests_import.xlsx
+++ b/RSVP_admin/assets/guests_import.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ADMIN\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\kimhy_invitation\invitation_03\RSVP_admin\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{590C6682-21AC-41D7-B505-E28E59793789}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9962F34-68F1-433D-808B-95ECBCAD1D8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{59DF4D0D-6DAE-4FC0-942D-1D87D9E8D967}"/>
+    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{59DF4D0D-6DAE-4FC0-942D-1D87D9E8D967}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="509" uniqueCount="344">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="530" uniqueCount="356">
   <si>
     <t>ma</t>
   </si>
@@ -66,12 +66,6 @@
     <t>B Long</t>
   </si>
   <si>
-    <t>B Thành (Tẻo)</t>
-  </si>
-  <si>
-    <t>A Thành (Luận)</t>
-  </si>
-  <si>
     <t>B Hưng</t>
   </si>
   <si>
@@ -165,117 +159,6 @@
     <t>dongnien_20</t>
   </si>
   <si>
-    <t>Thuấn</t>
-  </si>
-  <si>
-    <t>Hải</t>
-  </si>
-  <si>
-    <t>Hoàn</t>
-  </si>
-  <si>
-    <t>Thuỳ</t>
-  </si>
-  <si>
-    <t>Khánh</t>
-  </si>
-  <si>
-    <t>Tuấn</t>
-  </si>
-  <si>
-    <t>Bắc</t>
-  </si>
-  <si>
-    <t>Tuyển</t>
-  </si>
-  <si>
-    <t>Thông</t>
-  </si>
-  <si>
-    <t>Hùng</t>
-  </si>
-  <si>
-    <t>Thắng (Chiến)</t>
-  </si>
-  <si>
-    <t>Vân Anh</t>
-  </si>
-  <si>
-    <t>Thắng (Tân Thanh)</t>
-  </si>
-  <si>
-    <t>Sang</t>
-  </si>
-  <si>
-    <t>Hào</t>
-  </si>
-  <si>
-    <t>Duy</t>
-  </si>
-  <si>
-    <t>Thắm</t>
-  </si>
-  <si>
-    <t>Hậu</t>
-  </si>
-  <si>
-    <t>Hương</t>
-  </si>
-  <si>
-    <t>Quang Anh</t>
-  </si>
-  <si>
-    <t>Lanh</t>
-  </si>
-  <si>
-    <t>Huyền</t>
-  </si>
-  <si>
-    <t>Quế</t>
-  </si>
-  <si>
-    <t>Phương (nam)</t>
-  </si>
-  <si>
-    <t>Bích</t>
-  </si>
-  <si>
-    <t>Diễm A</t>
-  </si>
-  <si>
-    <t>Huế</t>
-  </si>
-  <si>
-    <t>Phương (nữ)</t>
-  </si>
-  <si>
-    <t>Lan</t>
-  </si>
-  <si>
-    <t>Quỳnh</t>
-  </si>
-  <si>
-    <t>Phúc</t>
-  </si>
-  <si>
-    <t>Hà</t>
-  </si>
-  <si>
-    <t>Tính</t>
-  </si>
-  <si>
-    <t>Trung Sơn</t>
-  </si>
-  <si>
-    <t>Thu Hiền</t>
-  </si>
-  <si>
-    <t>Sơn (Hoa)</t>
-  </si>
-  <si>
-    <t>Diễm B</t>
-  </si>
-  <si>
     <t>Đồng lớp</t>
   </si>
   <si>
@@ -438,9 +321,6 @@
     <t>B Phúc</t>
   </si>
   <si>
-    <t>B Hùng (Tân Yên)</t>
-  </si>
-  <si>
     <t>B Lan Anh</t>
   </si>
   <si>
@@ -846,12 +726,6 @@
     <t>A Tuấn Anh</t>
   </si>
   <si>
-    <t>Cháu  Hoàng (tuyến)</t>
-  </si>
-  <si>
-    <t>Cháu Tuấn (tuyên)</t>
-  </si>
-  <si>
     <t>E Hanh</t>
   </si>
   <si>
@@ -861,48 +735,12 @@
     <t>E Duy</t>
   </si>
   <si>
-    <t>E Hùng (Ốc)</t>
-  </si>
-  <si>
-    <t>E Tú (Thanh)</t>
-  </si>
-  <si>
-    <t>Cháu Cầu (Kỳ)</t>
-  </si>
-  <si>
-    <t>A Hạnh (Sông)</t>
-  </si>
-  <si>
-    <t>A Cường (Đồng)</t>
-  </si>
-  <si>
     <t>E Huyên</t>
   </si>
   <si>
-    <t>A Ánh (Thuỵ)</t>
-  </si>
-  <si>
     <t>E Sáng</t>
   </si>
   <si>
-    <t>E Thanh (Mích)</t>
-  </si>
-  <si>
-    <t>E Phương (Đông)</t>
-  </si>
-  <si>
-    <t>A Hưng (a trai Hải)</t>
-  </si>
-  <si>
-    <t>E Hiện (mợ Hoa)</t>
-  </si>
-  <si>
-    <t>A Cường (Thạch Thất)</t>
-  </si>
-  <si>
-    <t>A Minh (bác Tác)</t>
-  </si>
-  <si>
     <t>Ae trong làng</t>
   </si>
   <si>
@@ -1057,6 +895,204 @@
   </si>
   <si>
     <t>TraiNoi_03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B Thành </t>
+  </si>
+  <si>
+    <t xml:space="preserve">A Thành </t>
+  </si>
+  <si>
+    <t>B.Thuấn</t>
+  </si>
+  <si>
+    <t>B.Hải</t>
+  </si>
+  <si>
+    <t>B.Hoàn</t>
+  </si>
+  <si>
+    <t>B.Thuỳ</t>
+  </si>
+  <si>
+    <t>B.Khánh</t>
+  </si>
+  <si>
+    <t>B.Tuấn</t>
+  </si>
+  <si>
+    <t>B.Bắc</t>
+  </si>
+  <si>
+    <t>B.Tuyển</t>
+  </si>
+  <si>
+    <t>B.Thông</t>
+  </si>
+  <si>
+    <t>B.Hùng</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B.Thắng </t>
+  </si>
+  <si>
+    <t>B.Vân Anh</t>
+  </si>
+  <si>
+    <t>B.Sang</t>
+  </si>
+  <si>
+    <t>B.Hào</t>
+  </si>
+  <si>
+    <t>B.Duy</t>
+  </si>
+  <si>
+    <t>B.Thắm</t>
+  </si>
+  <si>
+    <t>B.Hậu</t>
+  </si>
+  <si>
+    <t>B.Hương</t>
+  </si>
+  <si>
+    <t>B.Quang Anh</t>
+  </si>
+  <si>
+    <t>B.Lanh</t>
+  </si>
+  <si>
+    <t>B.Huyền</t>
+  </si>
+  <si>
+    <t>B.Quế</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B.Phương </t>
+  </si>
+  <si>
+    <t>B.Bích</t>
+  </si>
+  <si>
+    <t>B.Diễm A</t>
+  </si>
+  <si>
+    <t>B.Huế</t>
+  </si>
+  <si>
+    <t>B.Lan</t>
+  </si>
+  <si>
+    <t>B.Quỳnh</t>
+  </si>
+  <si>
+    <t>B.Phúc</t>
+  </si>
+  <si>
+    <t>B.Hà</t>
+  </si>
+  <si>
+    <t>B.Tính</t>
+  </si>
+  <si>
+    <t>B.Trung Sơn</t>
+  </si>
+  <si>
+    <t>B.Thu Hiền</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B.Sơn </t>
+  </si>
+  <si>
+    <t>B.Diễm B</t>
+  </si>
+  <si>
+    <t>B Hùng</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cháu Hoàng </t>
+  </si>
+  <si>
+    <t>Cháu Tuấn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E Hùng </t>
+  </si>
+  <si>
+    <t>E Tú</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cháu Cầu </t>
+  </si>
+  <si>
+    <t xml:space="preserve">A Hạnh </t>
+  </si>
+  <si>
+    <t xml:space="preserve">A Cường </t>
+  </si>
+  <si>
+    <t xml:space="preserve">A Ánh </t>
+  </si>
+  <si>
+    <t xml:space="preserve">E Thanh </t>
+  </si>
+  <si>
+    <t xml:space="preserve">E Phương </t>
+  </si>
+  <si>
+    <t xml:space="preserve">A Hưng </t>
+  </si>
+  <si>
+    <t xml:space="preserve">E Hiện </t>
+  </si>
+  <si>
+    <t xml:space="preserve">A Minh </t>
+  </si>
+  <si>
+    <t xml:space="preserve">VK CK chị Quỳnh </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Em Thịnh </t>
+  </si>
+  <si>
+    <t>Dì Đan</t>
+  </si>
+  <si>
+    <t>Chị Phương</t>
+  </si>
+  <si>
+    <t>VK CK chị Hương</t>
+  </si>
+  <si>
+    <t>VK CK Chị Phi</t>
+  </si>
+  <si>
+    <t>Bạn Thảo (bên nhật)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VK CK Em Ngân </t>
+  </si>
+  <si>
+    <t>BanThao_01</t>
+  </si>
+  <si>
+    <t>BanThao_02</t>
+  </si>
+  <si>
+    <t>BanThao_03</t>
+  </si>
+  <si>
+    <t>BanThao_04</t>
+  </si>
+  <si>
+    <t>BanThao_05</t>
+  </si>
+  <si>
+    <t>BanThao_06</t>
+  </si>
+  <si>
+    <t>BanThao_07</t>
   </si>
 </sst>
 </file>
@@ -1112,7 +1148,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1428,12 +1464,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AC9DFBF0-824B-461B-9A24-F9A2CFE4B055}">
-  <dimension ref="A1:E169"/>
+  <dimension ref="A1:E176"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="16.796875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.69921875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.69921875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="11.796875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="12.3984375" bestFit="1" customWidth="1"/>
   </cols>
@@ -1457,13 +1493,13 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C2" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -1474,13 +1510,13 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>6</v>
       </c>
       <c r="C3" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D3">
         <v>1</v>
@@ -1491,13 +1527,13 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C4" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D4">
         <v>1</v>
@@ -1508,13 +1544,13 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C5" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D5">
         <v>1</v>
@@ -1525,13 +1561,13 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>9</v>
       </c>
       <c r="C6" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D6">
         <v>1</v>
@@ -1542,13 +1578,13 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C7" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D7">
         <v>1</v>
@@ -1559,13 +1595,13 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>11</v>
       </c>
       <c r="C8" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D8">
         <v>1</v>
@@ -1576,13 +1612,13 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C9" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D9">
         <v>1</v>
@@ -1593,13 +1629,13 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>13</v>
+        <v>290</v>
       </c>
       <c r="C10" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D10">
         <v>1</v>
@@ -1610,13 +1646,13 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>14</v>
+        <v>291</v>
       </c>
       <c r="C11" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D11">
         <v>1</v>
@@ -1627,13 +1663,13 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C12" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D12">
         <v>2</v>
@@ -1644,13 +1680,13 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C13" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D13">
         <v>2</v>
@@ -1661,13 +1697,13 @@
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C14" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D14">
         <v>2</v>
@@ -1678,13 +1714,13 @@
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C15" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D15">
         <v>2</v>
@@ -1695,13 +1731,13 @@
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C16" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D16">
         <v>2</v>
@@ -1712,13 +1748,13 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C17" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D17">
         <v>2</v>
@@ -1729,13 +1765,13 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C18" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D18">
         <v>2</v>
@@ -1746,13 +1782,13 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C19" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D19">
         <v>2</v>
@@ -1763,13 +1799,13 @@
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B20" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C20" t="s">
         <v>23</v>
-      </c>
-      <c r="C20" t="s">
-        <v>25</v>
       </c>
       <c r="D20">
         <v>2</v>
@@ -1780,13 +1816,13 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C21" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D21">
         <v>2</v>
@@ -1797,13 +1833,13 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>84</v>
+        <v>45</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>46</v>
+        <v>292</v>
       </c>
       <c r="C22" t="s">
-        <v>83</v>
+        <v>44</v>
       </c>
       <c r="D22">
         <v>3</v>
@@ -1814,13 +1850,13 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>85</v>
+        <v>46</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>47</v>
+        <v>293</v>
       </c>
       <c r="C23" t="s">
-        <v>83</v>
+        <v>44</v>
       </c>
       <c r="D23">
         <v>3</v>
@@ -1831,13 +1867,13 @@
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>86</v>
+        <v>47</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>48</v>
+        <v>294</v>
       </c>
       <c r="C24" t="s">
-        <v>83</v>
+        <v>44</v>
       </c>
       <c r="D24">
         <v>3</v>
@@ -1848,13 +1884,13 @@
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>87</v>
+        <v>48</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>49</v>
+        <v>295</v>
       </c>
       <c r="C25" t="s">
-        <v>83</v>
+        <v>44</v>
       </c>
       <c r="D25">
         <v>3</v>
@@ -1865,13 +1901,13 @@
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>88</v>
+        <v>49</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>50</v>
+        <v>296</v>
       </c>
       <c r="C26" t="s">
-        <v>83</v>
+        <v>44</v>
       </c>
       <c r="D26">
         <v>3</v>
@@ -1882,13 +1918,13 @@
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>89</v>
+        <v>50</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>51</v>
+        <v>297</v>
       </c>
       <c r="C27" t="s">
-        <v>83</v>
+        <v>44</v>
       </c>
       <c r="D27">
         <v>3</v>
@@ -1899,13 +1935,13 @@
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>90</v>
+        <v>51</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>52</v>
+        <v>298</v>
       </c>
       <c r="C28" t="s">
-        <v>83</v>
+        <v>44</v>
       </c>
       <c r="D28">
         <v>3</v>
@@ -1916,13 +1952,13 @@
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>91</v>
+        <v>52</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>53</v>
+        <v>299</v>
       </c>
       <c r="C29" t="s">
-        <v>83</v>
+        <v>44</v>
       </c>
       <c r="D29">
         <v>3</v>
@@ -1933,13 +1969,13 @@
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>92</v>
+        <v>53</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>54</v>
+        <v>300</v>
       </c>
       <c r="C30" t="s">
-        <v>83</v>
+        <v>44</v>
       </c>
       <c r="D30">
         <v>3</v>
@@ -1950,13 +1986,13 @@
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>93</v>
+        <v>54</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>55</v>
+        <v>301</v>
       </c>
       <c r="C31" t="s">
-        <v>83</v>
+        <v>44</v>
       </c>
       <c r="D31">
         <v>3</v>
@@ -1967,13 +2003,13 @@
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>94</v>
+        <v>55</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>56</v>
+        <v>302</v>
       </c>
       <c r="C32" t="s">
-        <v>83</v>
+        <v>44</v>
       </c>
       <c r="D32">
         <v>4</v>
@@ -1984,13 +2020,13 @@
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>95</v>
+        <v>56</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>57</v>
+        <v>303</v>
       </c>
       <c r="C33" t="s">
-        <v>83</v>
+        <v>44</v>
       </c>
       <c r="D33">
         <v>4</v>
@@ -2001,13 +2037,13 @@
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>96</v>
+        <v>57</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>58</v>
+        <v>302</v>
       </c>
       <c r="C34" t="s">
-        <v>83</v>
+        <v>44</v>
       </c>
       <c r="D34">
         <v>4</v>
@@ -2018,13 +2054,13 @@
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>97</v>
+        <v>58</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>59</v>
+        <v>304</v>
       </c>
       <c r="C35" t="s">
-        <v>83</v>
+        <v>44</v>
       </c>
       <c r="D35">
         <v>4</v>
@@ -2035,13 +2071,13 @@
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>98</v>
+        <v>59</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>60</v>
+        <v>305</v>
       </c>
       <c r="C36" t="s">
-        <v>83</v>
+        <v>44</v>
       </c>
       <c r="D36">
         <v>4</v>
@@ -2052,13 +2088,13 @@
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>99</v>
+        <v>60</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>61</v>
+        <v>306</v>
       </c>
       <c r="C37" t="s">
-        <v>83</v>
+        <v>44</v>
       </c>
       <c r="D37">
         <v>4</v>
@@ -2069,13 +2105,13 @@
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>100</v>
+        <v>61</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>62</v>
+        <v>307</v>
       </c>
       <c r="C38" t="s">
-        <v>83</v>
+        <v>44</v>
       </c>
       <c r="D38">
         <v>4</v>
@@ -2086,13 +2122,13 @@
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>101</v>
+        <v>62</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>63</v>
+        <v>308</v>
       </c>
       <c r="C39" t="s">
-        <v>83</v>
+        <v>44</v>
       </c>
       <c r="D39">
         <v>4</v>
@@ -2103,13 +2139,13 @@
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>102</v>
+        <v>63</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>64</v>
+        <v>309</v>
       </c>
       <c r="C40" t="s">
-        <v>83</v>
+        <v>44</v>
       </c>
       <c r="D40">
         <v>4</v>
@@ -2120,13 +2156,13 @@
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>103</v>
+        <v>64</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>65</v>
+        <v>310</v>
       </c>
       <c r="C41" t="s">
-        <v>83</v>
+        <v>44</v>
       </c>
       <c r="D41">
         <v>4</v>
@@ -2137,13 +2173,13 @@
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
-        <v>104</v>
+        <v>65</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>66</v>
+        <v>311</v>
       </c>
       <c r="C42" t="s">
-        <v>83</v>
+        <v>44</v>
       </c>
       <c r="D42">
         <v>5</v>
@@ -2154,13 +2190,13 @@
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
-        <v>105</v>
+        <v>66</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>67</v>
+        <v>312</v>
       </c>
       <c r="C43" t="s">
-        <v>83</v>
+        <v>44</v>
       </c>
       <c r="D43">
         <v>5</v>
@@ -2171,13 +2207,13 @@
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
-        <v>106</v>
+        <v>67</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>68</v>
+        <v>313</v>
       </c>
       <c r="C44" t="s">
-        <v>83</v>
+        <v>44</v>
       </c>
       <c r="D44">
         <v>5</v>
@@ -2188,13 +2224,13 @@
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
-        <v>107</v>
+        <v>68</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>69</v>
+        <v>314</v>
       </c>
       <c r="C45" t="s">
-        <v>83</v>
+        <v>44</v>
       </c>
       <c r="D45">
         <v>5</v>
@@ -2205,13 +2241,13 @@
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
-        <v>108</v>
+        <v>69</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>70</v>
+        <v>315</v>
       </c>
       <c r="C46" t="s">
-        <v>83</v>
+        <v>44</v>
       </c>
       <c r="D46">
         <v>5</v>
@@ -2222,13 +2258,13 @@
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
-        <v>109</v>
+        <v>70</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>71</v>
+        <v>316</v>
       </c>
       <c r="C47" t="s">
-        <v>83</v>
+        <v>44</v>
       </c>
       <c r="D47">
         <v>5</v>
@@ -2239,13 +2275,13 @@
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
-        <v>110</v>
+        <v>71</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>72</v>
+        <v>317</v>
       </c>
       <c r="C48" t="s">
-        <v>83</v>
+        <v>44</v>
       </c>
       <c r="D48">
         <v>5</v>
@@ -2256,13 +2292,13 @@
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
-        <v>111</v>
+        <v>72</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>73</v>
+        <v>314</v>
       </c>
       <c r="C49" t="s">
-        <v>83</v>
+        <v>44</v>
       </c>
       <c r="D49">
         <v>5</v>
@@ -2273,13 +2309,13 @@
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
-        <v>112</v>
+        <v>73</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>74</v>
+        <v>318</v>
       </c>
       <c r="C50" t="s">
-        <v>83</v>
+        <v>44</v>
       </c>
       <c r="D50">
         <v>5</v>
@@ -2290,13 +2326,13 @@
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
-        <v>113</v>
+        <v>74</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>75</v>
+        <v>319</v>
       </c>
       <c r="C51" t="s">
-        <v>83</v>
+        <v>44</v>
       </c>
       <c r="D51">
         <v>5</v>
@@ -2307,15 +2343,15 @@
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
-        <v>114</v>
+        <v>75</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>76</v>
+        <v>320</v>
       </c>
       <c r="C52" t="s">
-        <v>83</v>
-      </c>
-      <c r="D52" s="3">
+        <v>44</v>
+      </c>
+      <c r="D52">
         <v>6</v>
       </c>
       <c r="E52">
@@ -2324,15 +2360,15 @@
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
-        <v>115</v>
+        <v>76</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>77</v>
+        <v>321</v>
       </c>
       <c r="C53" t="s">
-        <v>83</v>
-      </c>
-      <c r="D53" s="3">
+        <v>44</v>
+      </c>
+      <c r="D53">
         <v>6</v>
       </c>
       <c r="E53">
@@ -2341,15 +2377,15 @@
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
-        <v>116</v>
+        <v>77</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>78</v>
+        <v>322</v>
       </c>
       <c r="C54" t="s">
-        <v>83</v>
-      </c>
-      <c r="D54" s="3">
+        <v>44</v>
+      </c>
+      <c r="D54">
         <v>6</v>
       </c>
       <c r="E54">
@@ -2358,15 +2394,15 @@
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
-        <v>117</v>
+        <v>78</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>79</v>
+        <v>323</v>
       </c>
       <c r="C55" t="s">
-        <v>83</v>
-      </c>
-      <c r="D55" s="3">
+        <v>44</v>
+      </c>
+      <c r="D55">
         <v>6</v>
       </c>
       <c r="E55">
@@ -2375,15 +2411,15 @@
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
-        <v>118</v>
+        <v>79</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>80</v>
+        <v>324</v>
       </c>
       <c r="C56" t="s">
-        <v>83</v>
-      </c>
-      <c r="D56" s="3">
+        <v>44</v>
+      </c>
+      <c r="D56">
         <v>6</v>
       </c>
       <c r="E56">
@@ -2392,15 +2428,15 @@
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
-        <v>119</v>
+        <v>80</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>81</v>
+        <v>325</v>
       </c>
       <c r="C57" t="s">
-        <v>83</v>
-      </c>
-      <c r="D57" s="3">
+        <v>44</v>
+      </c>
+      <c r="D57">
         <v>6</v>
       </c>
       <c r="E57">
@@ -2409,15 +2445,15 @@
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
-        <v>120</v>
+        <v>81</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>82</v>
+        <v>326</v>
       </c>
       <c r="C58" t="s">
-        <v>83</v>
-      </c>
-      <c r="D58" s="3">
+        <v>44</v>
+      </c>
+      <c r="D58">
         <v>6</v>
       </c>
       <c r="E58">
@@ -2426,13 +2462,13 @@
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
-        <v>126</v>
+        <v>87</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>121</v>
+        <v>82</v>
       </c>
       <c r="C59" t="s">
-        <v>125</v>
+        <v>86</v>
       </c>
       <c r="D59">
         <v>7</v>
@@ -2443,13 +2479,13 @@
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
-        <v>127</v>
+        <v>88</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>122</v>
+        <v>83</v>
       </c>
       <c r="C60" t="s">
-        <v>125</v>
+        <v>86</v>
       </c>
       <c r="D60">
         <v>7</v>
@@ -2460,13 +2496,13 @@
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
-        <v>128</v>
+        <v>89</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>123</v>
+        <v>84</v>
       </c>
       <c r="C61" t="s">
-        <v>125</v>
+        <v>86</v>
       </c>
       <c r="D61">
         <v>7</v>
@@ -2477,13 +2513,13 @@
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
-        <v>129</v>
+        <v>90</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>124</v>
+        <v>85</v>
       </c>
       <c r="C62" t="s">
-        <v>125</v>
+        <v>86</v>
       </c>
       <c r="D62">
         <v>7</v>
@@ -2494,13 +2530,13 @@
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
-        <v>140</v>
+        <v>100</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>130</v>
+        <v>91</v>
       </c>
       <c r="C63" t="s">
-        <v>151</v>
+        <v>111</v>
       </c>
       <c r="D63">
         <v>7</v>
@@ -2511,13 +2547,13 @@
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
-        <v>141</v>
+        <v>101</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>131</v>
+        <v>92</v>
       </c>
       <c r="C64" t="s">
-        <v>151</v>
+        <v>111</v>
       </c>
       <c r="D64">
         <v>7</v>
@@ -2528,13 +2564,13 @@
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
-        <v>142</v>
+        <v>102</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>132</v>
+        <v>93</v>
       </c>
       <c r="C65" t="s">
-        <v>151</v>
+        <v>111</v>
       </c>
       <c r="D65">
         <v>7</v>
@@ -2545,13 +2581,13 @@
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
-        <v>143</v>
+        <v>103</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>133</v>
+        <v>94</v>
       </c>
       <c r="C66" t="s">
-        <v>151</v>
+        <v>111</v>
       </c>
       <c r="D66">
         <v>7</v>
@@ -2562,13 +2598,13 @@
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
-        <v>144</v>
+        <v>104</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>134</v>
+        <v>95</v>
       </c>
       <c r="C67" t="s">
-        <v>151</v>
+        <v>111</v>
       </c>
       <c r="D67">
         <v>7</v>
@@ -2579,13 +2615,13 @@
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
-        <v>145</v>
+        <v>105</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>135</v>
+        <v>96</v>
       </c>
       <c r="C68" t="s">
-        <v>151</v>
+        <v>111</v>
       </c>
       <c r="D68">
         <v>7</v>
@@ -2596,13 +2632,13 @@
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
-        <v>146</v>
+        <v>106</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>136</v>
+        <v>97</v>
       </c>
       <c r="C69" t="s">
-        <v>151</v>
+        <v>111</v>
       </c>
       <c r="D69">
         <v>6</v>
@@ -2613,13 +2649,13 @@
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
-        <v>147</v>
+        <v>107</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>137</v>
+        <v>327</v>
       </c>
       <c r="C70" t="s">
-        <v>151</v>
+        <v>111</v>
       </c>
       <c r="D70">
         <v>6</v>
@@ -2630,13 +2666,13 @@
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
-        <v>148</v>
+        <v>108</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>138</v>
+        <v>98</v>
       </c>
       <c r="C71" t="s">
-        <v>151</v>
+        <v>111</v>
       </c>
       <c r="D71">
         <v>6</v>
@@ -2647,13 +2683,13 @@
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
-        <v>149</v>
+        <v>109</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>139</v>
+        <v>99</v>
       </c>
       <c r="C72" t="s">
-        <v>151</v>
+        <v>111</v>
       </c>
       <c r="D72">
         <v>17</v>
@@ -2664,13 +2700,13 @@
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
-        <v>150</v>
+        <v>110</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C73" t="s">
-        <v>151</v>
+        <v>111</v>
       </c>
       <c r="D73">
         <v>9</v>
@@ -2681,13 +2717,13 @@
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
-        <v>161</v>
+        <v>121</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>152</v>
+        <v>112</v>
       </c>
       <c r="C74" t="s">
-        <v>160</v>
+        <v>120</v>
       </c>
       <c r="D74">
         <v>9</v>
@@ -2698,13 +2734,13 @@
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
-        <v>162</v>
+        <v>122</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>153</v>
+        <v>113</v>
       </c>
       <c r="C75" t="s">
-        <v>160</v>
+        <v>120</v>
       </c>
       <c r="D75">
         <v>9</v>
@@ -2715,13 +2751,13 @@
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
-        <v>163</v>
+        <v>123</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>154</v>
+        <v>114</v>
       </c>
       <c r="C76" t="s">
-        <v>160</v>
+        <v>120</v>
       </c>
       <c r="D76">
         <v>9</v>
@@ -2732,13 +2768,13 @@
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
-        <v>164</v>
+        <v>124</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>155</v>
+        <v>115</v>
       </c>
       <c r="C77" t="s">
-        <v>160</v>
+        <v>120</v>
       </c>
       <c r="D77">
         <v>9</v>
@@ -2749,13 +2785,13 @@
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
-        <v>165</v>
+        <v>125</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>156</v>
+        <v>116</v>
       </c>
       <c r="C78" t="s">
-        <v>160</v>
+        <v>120</v>
       </c>
       <c r="D78">
         <v>9</v>
@@ -2766,13 +2802,13 @@
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
-        <v>166</v>
+        <v>126</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>157</v>
+        <v>117</v>
       </c>
       <c r="C79" t="s">
-        <v>160</v>
+        <v>120</v>
       </c>
       <c r="D79">
         <v>9</v>
@@ -2783,13 +2819,13 @@
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
-        <v>167</v>
+        <v>127</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>158</v>
+        <v>118</v>
       </c>
       <c r="C80" t="s">
-        <v>160</v>
+        <v>120</v>
       </c>
       <c r="D80">
         <v>9</v>
@@ -2800,13 +2836,13 @@
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
-        <v>168</v>
+        <v>128</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>159</v>
+        <v>119</v>
       </c>
       <c r="C81" t="s">
-        <v>160</v>
+        <v>120</v>
       </c>
       <c r="D81">
         <v>9</v>
@@ -2817,13 +2853,13 @@
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
-        <v>169</v>
+        <v>129</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C82" t="s">
-        <v>160</v>
+        <v>120</v>
       </c>
       <c r="D82">
         <v>9</v>
@@ -2834,13 +2870,13 @@
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
-        <v>176</v>
+        <v>136</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>170</v>
+        <v>130</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>175</v>
+        <v>135</v>
       </c>
       <c r="D83">
         <v>11</v>
@@ -2851,13 +2887,13 @@
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
-        <v>177</v>
+        <v>137</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>171</v>
+        <v>131</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>175</v>
+        <v>135</v>
       </c>
       <c r="D84">
         <v>11</v>
@@ -2868,13 +2904,13 @@
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
-        <v>178</v>
+        <v>138</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>172</v>
+        <v>132</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>175</v>
+        <v>135</v>
       </c>
       <c r="D85">
         <v>11</v>
@@ -2885,13 +2921,13 @@
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
-        <v>179</v>
+        <v>139</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>173</v>
+        <v>133</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>175</v>
+        <v>135</v>
       </c>
       <c r="D86">
         <v>13</v>
@@ -2902,13 +2938,13 @@
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
-        <v>180</v>
+        <v>140</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>174</v>
+        <v>134</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>175</v>
+        <v>135</v>
       </c>
       <c r="D87">
         <v>8</v>
@@ -2919,13 +2955,13 @@
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A88" s="2" t="s">
-        <v>190</v>
+        <v>150</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>171</v>
+        <v>131</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>189</v>
+        <v>149</v>
       </c>
       <c r="D88">
         <v>8</v>
@@ -2936,13 +2972,13 @@
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A89" s="2" t="s">
-        <v>191</v>
+        <v>151</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>181</v>
+        <v>141</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>189</v>
+        <v>149</v>
       </c>
       <c r="D89">
         <v>8</v>
@@ -2953,13 +2989,13 @@
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A90" s="2" t="s">
-        <v>192</v>
+        <v>152</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>182</v>
+        <v>142</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>189</v>
+        <v>149</v>
       </c>
       <c r="D90">
         <v>8</v>
@@ -2970,13 +3006,13 @@
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A91" s="2" t="s">
-        <v>193</v>
+        <v>153</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>183</v>
+        <v>143</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>189</v>
+        <v>149</v>
       </c>
       <c r="D91">
         <v>8</v>
@@ -2987,13 +3023,13 @@
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A92" s="2" t="s">
-        <v>194</v>
+        <v>154</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>184</v>
+        <v>144</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>189</v>
+        <v>149</v>
       </c>
       <c r="D92">
         <v>8</v>
@@ -3004,13 +3040,13 @@
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A93" s="2" t="s">
-        <v>195</v>
+        <v>155</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>185</v>
+        <v>145</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>189</v>
+        <v>149</v>
       </c>
       <c r="D93">
         <v>8</v>
@@ -3021,13 +3057,13 @@
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A94" s="2" t="s">
-        <v>196</v>
+        <v>156</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>186</v>
+        <v>146</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>189</v>
+        <v>149</v>
       </c>
       <c r="D94">
         <v>8</v>
@@ -3038,13 +3074,13 @@
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A95" s="2" t="s">
-        <v>197</v>
+        <v>157</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>187</v>
+        <v>147</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>189</v>
+        <v>149</v>
       </c>
       <c r="D95">
         <v>8</v>
@@ -3055,13 +3091,13 @@
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A96" s="2" t="s">
-        <v>198</v>
+        <v>158</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>188</v>
+        <v>148</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>189</v>
+        <v>149</v>
       </c>
       <c r="D96">
         <v>8</v>
@@ -3072,13 +3108,13 @@
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A97" s="2" t="s">
-        <v>217</v>
+        <v>177</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>199</v>
+        <v>159</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>216</v>
+        <v>176</v>
       </c>
       <c r="D97">
         <v>10</v>
@@ -3089,13 +3125,13 @@
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A98" s="2" t="s">
-        <v>218</v>
+        <v>178</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>200</v>
+        <v>160</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>216</v>
+        <v>176</v>
       </c>
       <c r="D98">
         <v>10</v>
@@ -3106,13 +3142,13 @@
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A99" s="2" t="s">
-        <v>219</v>
+        <v>179</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>201</v>
+        <v>161</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>216</v>
+        <v>176</v>
       </c>
       <c r="D99">
         <v>10</v>
@@ -3123,13 +3159,13 @@
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A100" s="2" t="s">
-        <v>220</v>
+        <v>180</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>202</v>
+        <v>162</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>216</v>
+        <v>176</v>
       </c>
       <c r="D100">
         <v>10</v>
@@ -3140,13 +3176,13 @@
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A101" s="2" t="s">
-        <v>221</v>
+        <v>181</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>203</v>
+        <v>163</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>216</v>
+        <v>176</v>
       </c>
       <c r="D101">
         <v>10</v>
@@ -3157,13 +3193,13 @@
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A102" s="2" t="s">
-        <v>222</v>
+        <v>182</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>204</v>
+        <v>164</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>216</v>
+        <v>176</v>
       </c>
       <c r="D102">
         <v>10</v>
@@ -3174,13 +3210,13 @@
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A103" s="2" t="s">
-        <v>223</v>
+        <v>183</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>205</v>
+        <v>165</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>216</v>
+        <v>176</v>
       </c>
       <c r="D103">
         <v>10</v>
@@ -3191,13 +3227,13 @@
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A104" s="2" t="s">
-        <v>224</v>
+        <v>184</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>206</v>
+        <v>166</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>216</v>
+        <v>176</v>
       </c>
       <c r="D104">
         <v>10</v>
@@ -3208,13 +3244,13 @@
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A105" s="2" t="s">
-        <v>225</v>
+        <v>185</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>207</v>
+        <v>167</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>216</v>
+        <v>176</v>
       </c>
       <c r="D105">
         <v>10</v>
@@ -3225,13 +3261,13 @@
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A106" s="2" t="s">
-        <v>226</v>
+        <v>186</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>208</v>
+        <v>168</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>216</v>
+        <v>176</v>
       </c>
       <c r="D106">
         <v>10</v>
@@ -3242,13 +3278,13 @@
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A107" s="2" t="s">
-        <v>227</v>
+        <v>187</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>209</v>
+        <v>169</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>216</v>
+        <v>176</v>
       </c>
       <c r="D107">
         <v>11</v>
@@ -3259,13 +3295,13 @@
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A108" s="2" t="s">
-        <v>228</v>
+        <v>188</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>210</v>
+        <v>170</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>216</v>
+        <v>176</v>
       </c>
       <c r="D108">
         <v>11</v>
@@ -3276,13 +3312,13 @@
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A109" s="2" t="s">
-        <v>229</v>
+        <v>189</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>211</v>
+        <v>171</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>216</v>
+        <v>176</v>
       </c>
       <c r="D109">
         <v>11</v>
@@ -3293,13 +3329,13 @@
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A110" s="2" t="s">
-        <v>230</v>
+        <v>190</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>212</v>
+        <v>172</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>216</v>
+        <v>176</v>
       </c>
       <c r="D110">
         <v>11</v>
@@ -3310,13 +3346,13 @@
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A111" s="2" t="s">
-        <v>231</v>
+        <v>191</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>213</v>
+        <v>173</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>216</v>
+        <v>176</v>
       </c>
       <c r="D111">
         <v>11</v>
@@ -3327,13 +3363,13 @@
     </row>
     <row r="112" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A112" s="2" t="s">
-        <v>232</v>
+        <v>192</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>214</v>
+        <v>174</v>
       </c>
       <c r="C112" s="2" t="s">
-        <v>216</v>
+        <v>176</v>
       </c>
       <c r="D112">
         <v>11</v>
@@ -3344,13 +3380,13 @@
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A113" s="2" t="s">
-        <v>233</v>
+        <v>193</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>215</v>
+        <v>175</v>
       </c>
       <c r="C113" s="2" t="s">
-        <v>216</v>
+        <v>176</v>
       </c>
       <c r="D113">
         <v>11</v>
@@ -3361,13 +3397,13 @@
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A114" s="2" t="s">
-        <v>238</v>
+        <v>198</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>234</v>
+        <v>194</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>237</v>
+        <v>197</v>
       </c>
       <c r="D114">
         <v>13</v>
@@ -3378,13 +3414,13 @@
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A115" s="2" t="s">
-        <v>239</v>
+        <v>199</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>184</v>
+        <v>144</v>
       </c>
       <c r="C115" s="2" t="s">
-        <v>237</v>
+        <v>197</v>
       </c>
       <c r="D115">
         <v>13</v>
@@ -3395,13 +3431,13 @@
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A116" s="2" t="s">
-        <v>240</v>
+        <v>200</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>235</v>
+        <v>195</v>
       </c>
       <c r="C116" s="2" t="s">
-        <v>237</v>
+        <v>197</v>
       </c>
       <c r="D116">
         <v>13</v>
@@ -3412,13 +3448,13 @@
     </row>
     <row r="117" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A117" s="2" t="s">
-        <v>241</v>
+        <v>201</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>236</v>
+        <v>196</v>
       </c>
       <c r="C117" s="2" t="s">
-        <v>237</v>
+        <v>197</v>
       </c>
       <c r="D117">
         <v>13</v>
@@ -3429,13 +3465,13 @@
     </row>
     <row r="118" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A118" s="2" t="s">
-        <v>251</v>
+        <v>211</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>155</v>
+        <v>115</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>242</v>
+        <v>202</v>
       </c>
       <c r="D118">
         <v>12</v>
@@ -3446,13 +3482,13 @@
     </row>
     <row r="119" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A119" s="2" t="s">
-        <v>252</v>
+        <v>212</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>243</v>
+        <v>203</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>242</v>
+        <v>202</v>
       </c>
       <c r="D119">
         <v>12</v>
@@ -3463,13 +3499,13 @@
     </row>
     <row r="120" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A120" s="2" t="s">
-        <v>253</v>
+        <v>213</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>184</v>
+        <v>144</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>242</v>
+        <v>202</v>
       </c>
       <c r="D120">
         <v>12</v>
@@ -3480,13 +3516,13 @@
     </row>
     <row r="121" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A121" s="2" t="s">
-        <v>254</v>
+        <v>214</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>244</v>
+        <v>204</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>242</v>
+        <v>202</v>
       </c>
       <c r="D121">
         <v>12</v>
@@ -3497,13 +3533,13 @@
     </row>
     <row r="122" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A122" s="2" t="s">
-        <v>255</v>
+        <v>215</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>245</v>
+        <v>205</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>242</v>
+        <v>202</v>
       </c>
       <c r="D122">
         <v>12</v>
@@ -3514,13 +3550,13 @@
     </row>
     <row r="123" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A123" s="2" t="s">
-        <v>256</v>
+        <v>216</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>246</v>
+        <v>206</v>
       </c>
       <c r="C123" s="2" t="s">
-        <v>242</v>
+        <v>202</v>
       </c>
       <c r="D123">
         <v>12</v>
@@ -3531,13 +3567,13 @@
     </row>
     <row r="124" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A124" s="2" t="s">
-        <v>257</v>
+        <v>217</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>247</v>
+        <v>207</v>
       </c>
       <c r="C124" s="2" t="s">
-        <v>242</v>
+        <v>202</v>
       </c>
       <c r="D124">
         <v>12</v>
@@ -3548,13 +3584,13 @@
     </row>
     <row r="125" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A125" s="2" t="s">
-        <v>258</v>
+        <v>218</v>
       </c>
       <c r="B125" s="2" t="s">
-        <v>248</v>
+        <v>208</v>
       </c>
       <c r="C125" s="2" t="s">
-        <v>242</v>
+        <v>202</v>
       </c>
       <c r="D125">
         <v>12</v>
@@ -3565,13 +3601,13 @@
     </row>
     <row r="126" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A126" s="2" t="s">
-        <v>259</v>
+        <v>219</v>
       </c>
       <c r="B126" s="2" t="s">
-        <v>249</v>
+        <v>209</v>
       </c>
       <c r="C126" s="2" t="s">
-        <v>242</v>
+        <v>202</v>
       </c>
       <c r="D126">
         <v>12</v>
@@ -3582,13 +3618,13 @@
     </row>
     <row r="127" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A127" s="2" t="s">
-        <v>260</v>
+        <v>220</v>
       </c>
       <c r="B127" s="2" t="s">
-        <v>250</v>
+        <v>210</v>
       </c>
       <c r="C127" s="2" t="s">
-        <v>242</v>
+        <v>202</v>
       </c>
       <c r="D127">
         <v>12</v>
@@ -3599,13 +3635,13 @@
     </row>
     <row r="128" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A128" s="2" t="s">
-        <v>267</v>
+        <v>227</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>261</v>
+        <v>221</v>
       </c>
       <c r="C128" s="2" t="s">
-        <v>266</v>
+        <v>226</v>
       </c>
       <c r="D128">
         <v>13</v>
@@ -3616,13 +3652,13 @@
     </row>
     <row r="129" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A129" s="2" t="s">
-        <v>268</v>
+        <v>228</v>
       </c>
       <c r="B129" s="2" t="s">
-        <v>262</v>
+        <v>222</v>
       </c>
       <c r="C129" s="2" t="s">
-        <v>266</v>
+        <v>226</v>
       </c>
       <c r="D129">
         <v>13</v>
@@ -3633,13 +3669,13 @@
     </row>
     <row r="130" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A130" s="2" t="s">
-        <v>269</v>
+        <v>229</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>263</v>
+        <v>223</v>
       </c>
       <c r="C130" s="2" t="s">
-        <v>266</v>
+        <v>226</v>
       </c>
       <c r="D130">
         <v>13</v>
@@ -3650,13 +3686,13 @@
     </row>
     <row r="131" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A131" s="2" t="s">
-        <v>270</v>
+        <v>230</v>
       </c>
       <c r="B131" s="2" t="s">
-        <v>264</v>
+        <v>224</v>
       </c>
       <c r="C131" s="2" t="s">
-        <v>266</v>
+        <v>226</v>
       </c>
       <c r="D131">
         <v>13</v>
@@ -3667,13 +3703,13 @@
     </row>
     <row r="132" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A132" s="2" t="s">
-        <v>271</v>
+        <v>231</v>
       </c>
       <c r="B132" s="2" t="s">
-        <v>265</v>
+        <v>225</v>
       </c>
       <c r="C132" s="2" t="s">
-        <v>266</v>
+        <v>226</v>
       </c>
       <c r="D132">
         <v>13</v>
@@ -3684,13 +3720,13 @@
     </row>
     <row r="133" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A133" s="2" t="s">
-        <v>293</v>
+        <v>239</v>
       </c>
       <c r="B133" s="2" t="s">
-        <v>185</v>
+        <v>145</v>
       </c>
       <c r="C133" s="2" t="s">
-        <v>292</v>
+        <v>238</v>
       </c>
       <c r="D133">
         <v>14</v>
@@ -3701,13 +3737,13 @@
     </row>
     <row r="134" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A134" s="2" t="s">
-        <v>294</v>
+        <v>240</v>
       </c>
       <c r="B134" s="2" t="s">
-        <v>155</v>
+        <v>115</v>
       </c>
       <c r="C134" s="2" t="s">
-        <v>292</v>
+        <v>238</v>
       </c>
       <c r="D134">
         <v>14</v>
@@ -3718,13 +3754,13 @@
     </row>
     <row r="135" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A135" s="2" t="s">
-        <v>295</v>
+        <v>241</v>
       </c>
       <c r="B135" s="2" t="s">
-        <v>272</v>
+        <v>232</v>
       </c>
       <c r="C135" s="2" t="s">
-        <v>292</v>
+        <v>238</v>
       </c>
       <c r="D135">
         <v>14</v>
@@ -3735,13 +3771,13 @@
     </row>
     <row r="136" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A136" s="2" t="s">
-        <v>296</v>
+        <v>242</v>
       </c>
       <c r="B136" s="2" t="s">
-        <v>273</v>
+        <v>328</v>
       </c>
       <c r="C136" s="2" t="s">
-        <v>292</v>
+        <v>238</v>
       </c>
       <c r="D136">
         <v>14</v>
@@ -3752,13 +3788,13 @@
     </row>
     <row r="137" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A137" s="2" t="s">
-        <v>297</v>
+        <v>243</v>
       </c>
       <c r="B137" s="2" t="s">
-        <v>274</v>
+        <v>329</v>
       </c>
       <c r="C137" s="2" t="s">
-        <v>292</v>
+        <v>238</v>
       </c>
       <c r="D137">
         <v>14</v>
@@ -3769,13 +3805,13 @@
     </row>
     <row r="138" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A138" s="2" t="s">
-        <v>298</v>
+        <v>244</v>
       </c>
       <c r="B138" s="2" t="s">
-        <v>275</v>
+        <v>233</v>
       </c>
       <c r="C138" s="2" t="s">
-        <v>292</v>
+        <v>238</v>
       </c>
       <c r="D138">
         <v>14</v>
@@ -3786,13 +3822,13 @@
     </row>
     <row r="139" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A139" s="2" t="s">
-        <v>299</v>
+        <v>245</v>
       </c>
       <c r="B139" s="2" t="s">
-        <v>204</v>
+        <v>164</v>
       </c>
       <c r="C139" s="2" t="s">
-        <v>292</v>
+        <v>238</v>
       </c>
       <c r="D139">
         <v>14</v>
@@ -3803,13 +3839,13 @@
     </row>
     <row r="140" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A140" s="2" t="s">
-        <v>300</v>
+        <v>246</v>
       </c>
       <c r="B140" s="2" t="s">
-        <v>276</v>
+        <v>234</v>
       </c>
       <c r="C140" s="2" t="s">
-        <v>292</v>
+        <v>238</v>
       </c>
       <c r="D140">
         <v>14</v>
@@ -3820,13 +3856,13 @@
     </row>
     <row r="141" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A141" s="2" t="s">
-        <v>301</v>
+        <v>247</v>
       </c>
       <c r="B141" s="2" t="s">
-        <v>277</v>
+        <v>235</v>
       </c>
       <c r="C141" s="2" t="s">
-        <v>292</v>
+        <v>238</v>
       </c>
       <c r="D141">
         <v>14</v>
@@ -3837,13 +3873,13 @@
     </row>
     <row r="142" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A142" s="2" t="s">
-        <v>302</v>
+        <v>248</v>
       </c>
       <c r="B142" s="2" t="s">
-        <v>278</v>
+        <v>330</v>
       </c>
       <c r="C142" s="2" t="s">
-        <v>292</v>
+        <v>238</v>
       </c>
       <c r="D142">
         <v>14</v>
@@ -3854,13 +3890,13 @@
     </row>
     <row r="143" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A143" s="2" t="s">
-        <v>303</v>
+        <v>249</v>
       </c>
       <c r="B143" s="2" t="s">
-        <v>279</v>
+        <v>331</v>
       </c>
       <c r="C143" s="2" t="s">
-        <v>292</v>
+        <v>238</v>
       </c>
       <c r="D143">
         <v>15</v>
@@ -3871,13 +3907,13 @@
     </row>
     <row r="144" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A144" s="2" t="s">
-        <v>304</v>
+        <v>250</v>
       </c>
       <c r="B144" s="2" t="s">
-        <v>280</v>
+        <v>332</v>
       </c>
       <c r="C144" s="2" t="s">
-        <v>292</v>
+        <v>238</v>
       </c>
       <c r="D144">
         <v>15</v>
@@ -3888,13 +3924,13 @@
     </row>
     <row r="145" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A145" s="2" t="s">
-        <v>305</v>
+        <v>251</v>
       </c>
       <c r="B145" s="2" t="s">
-        <v>281</v>
+        <v>333</v>
       </c>
       <c r="C145" s="2" t="s">
-        <v>292</v>
+        <v>238</v>
       </c>
       <c r="D145">
         <v>15</v>
@@ -3905,13 +3941,13 @@
     </row>
     <row r="146" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A146" s="2" t="s">
-        <v>306</v>
+        <v>252</v>
       </c>
       <c r="B146" s="2" t="s">
-        <v>282</v>
+        <v>334</v>
       </c>
       <c r="C146" s="2" t="s">
-        <v>292</v>
+        <v>238</v>
       </c>
       <c r="D146">
         <v>15</v>
@@ -3922,13 +3958,13 @@
     </row>
     <row r="147" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A147" s="2" t="s">
-        <v>307</v>
+        <v>253</v>
       </c>
       <c r="B147" s="2" t="s">
-        <v>283</v>
+        <v>236</v>
       </c>
       <c r="C147" s="2" t="s">
-        <v>292</v>
+        <v>238</v>
       </c>
       <c r="D147">
         <v>15</v>
@@ -3939,13 +3975,13 @@
     </row>
     <row r="148" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A148" s="2" t="s">
-        <v>308</v>
+        <v>254</v>
       </c>
       <c r="B148" s="2" t="s">
-        <v>284</v>
+        <v>335</v>
       </c>
       <c r="C148" s="2" t="s">
-        <v>292</v>
+        <v>238</v>
       </c>
       <c r="D148">
         <v>15</v>
@@ -3956,13 +3992,13 @@
     </row>
     <row r="149" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A149" s="2" t="s">
-        <v>309</v>
+        <v>255</v>
       </c>
       <c r="B149" s="2" t="s">
-        <v>285</v>
+        <v>237</v>
       </c>
       <c r="C149" s="2" t="s">
-        <v>292</v>
+        <v>238</v>
       </c>
       <c r="D149">
         <v>15</v>
@@ -3973,13 +4009,13 @@
     </row>
     <row r="150" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A150" s="2" t="s">
-        <v>310</v>
+        <v>256</v>
       </c>
       <c r="B150" s="2" t="s">
-        <v>286</v>
+        <v>336</v>
       </c>
       <c r="C150" s="2" t="s">
-        <v>292</v>
+        <v>238</v>
       </c>
       <c r="D150">
         <v>15</v>
@@ -3990,13 +4026,13 @@
     </row>
     <row r="151" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A151" s="2" t="s">
-        <v>311</v>
+        <v>257</v>
       </c>
       <c r="B151" s="2" t="s">
-        <v>287</v>
+        <v>337</v>
       </c>
       <c r="C151" s="2" t="s">
-        <v>292</v>
+        <v>238</v>
       </c>
       <c r="D151">
         <v>15</v>
@@ -4007,13 +4043,13 @@
     </row>
     <row r="152" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A152" s="2" t="s">
-        <v>312</v>
+        <v>258</v>
       </c>
       <c r="B152" s="2" t="s">
-        <v>288</v>
+        <v>338</v>
       </c>
       <c r="C152" s="2" t="s">
-        <v>292</v>
+        <v>238</v>
       </c>
       <c r="D152">
         <v>15</v>
@@ -4024,13 +4060,13 @@
     </row>
     <row r="153" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A153" s="2" t="s">
-        <v>313</v>
+        <v>259</v>
       </c>
       <c r="B153" s="2" t="s">
-        <v>289</v>
+        <v>339</v>
       </c>
       <c r="C153" s="2" t="s">
-        <v>292</v>
+        <v>238</v>
       </c>
       <c r="D153">
         <v>17</v>
@@ -4041,13 +4077,13 @@
     </row>
     <row r="154" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A154" s="2" t="s">
-        <v>314</v>
+        <v>260</v>
       </c>
       <c r="B154" s="2" t="s">
-        <v>290</v>
+        <v>334</v>
       </c>
       <c r="C154" s="2" t="s">
-        <v>292</v>
+        <v>238</v>
       </c>
       <c r="D154">
         <v>17</v>
@@ -4058,13 +4094,13 @@
     </row>
     <row r="155" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A155" s="2" t="s">
-        <v>315</v>
+        <v>261</v>
       </c>
       <c r="B155" s="2" t="s">
-        <v>291</v>
+        <v>340</v>
       </c>
       <c r="C155" s="2" t="s">
-        <v>292</v>
+        <v>238</v>
       </c>
       <c r="D155">
         <v>17</v>
@@ -4075,13 +4111,13 @@
     </row>
     <row r="156" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A156" s="2" t="s">
-        <v>326</v>
+        <v>272</v>
       </c>
       <c r="B156" s="2" t="s">
-        <v>316</v>
+        <v>262</v>
       </c>
       <c r="C156" s="2" t="s">
-        <v>325</v>
+        <v>271</v>
       </c>
       <c r="D156">
         <v>16</v>
@@ -4092,13 +4128,13 @@
     </row>
     <row r="157" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A157" s="2" t="s">
-        <v>327</v>
+        <v>273</v>
       </c>
       <c r="B157" s="2" t="s">
-        <v>317</v>
+        <v>263</v>
       </c>
       <c r="C157" s="2" t="s">
-        <v>325</v>
+        <v>271</v>
       </c>
       <c r="D157">
         <v>16</v>
@@ -4109,13 +4145,13 @@
     </row>
     <row r="158" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A158" s="2" t="s">
-        <v>328</v>
+        <v>274</v>
       </c>
       <c r="B158" s="2" t="s">
-        <v>318</v>
+        <v>264</v>
       </c>
       <c r="C158" s="2" t="s">
-        <v>325</v>
+        <v>271</v>
       </c>
       <c r="D158">
         <v>16</v>
@@ -4126,13 +4162,13 @@
     </row>
     <row r="159" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A159" s="2" t="s">
-        <v>329</v>
+        <v>275</v>
       </c>
       <c r="B159" s="2" t="s">
-        <v>246</v>
+        <v>206</v>
       </c>
       <c r="C159" s="2" t="s">
-        <v>325</v>
+        <v>271</v>
       </c>
       <c r="D159">
         <v>16</v>
@@ -4143,13 +4179,13 @@
     </row>
     <row r="160" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A160" s="2" t="s">
-        <v>330</v>
+        <v>276</v>
       </c>
       <c r="B160" s="2" t="s">
-        <v>319</v>
+        <v>265</v>
       </c>
       <c r="C160" s="2" t="s">
-        <v>325</v>
+        <v>271</v>
       </c>
       <c r="D160">
         <v>16</v>
@@ -4160,13 +4196,13 @@
     </row>
     <row r="161" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A161" s="2" t="s">
-        <v>331</v>
+        <v>277</v>
       </c>
       <c r="B161" s="2" t="s">
-        <v>320</v>
+        <v>266</v>
       </c>
       <c r="C161" s="2" t="s">
-        <v>325</v>
+        <v>271</v>
       </c>
       <c r="D161">
         <v>16</v>
@@ -4177,13 +4213,13 @@
     </row>
     <row r="162" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A162" s="2" t="s">
-        <v>332</v>
+        <v>278</v>
       </c>
       <c r="B162" s="2" t="s">
-        <v>321</v>
+        <v>267</v>
       </c>
       <c r="C162" s="2" t="s">
-        <v>325</v>
+        <v>271</v>
       </c>
       <c r="D162">
         <v>16</v>
@@ -4194,13 +4230,13 @@
     </row>
     <row r="163" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A163" s="2" t="s">
-        <v>333</v>
+        <v>279</v>
       </c>
       <c r="B163" s="2" t="s">
-        <v>153</v>
+        <v>113</v>
       </c>
       <c r="C163" s="2" t="s">
-        <v>325</v>
+        <v>271</v>
       </c>
       <c r="D163">
         <v>16</v>
@@ -4211,13 +4247,13 @@
     </row>
     <row r="164" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A164" s="2" t="s">
-        <v>334</v>
+        <v>280</v>
       </c>
       <c r="B164" s="2" t="s">
-        <v>322</v>
+        <v>268</v>
       </c>
       <c r="C164" s="2" t="s">
-        <v>325</v>
+        <v>271</v>
       </c>
       <c r="D164">
         <v>16</v>
@@ -4228,13 +4264,13 @@
     </row>
     <row r="165" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A165" s="2" t="s">
-        <v>335</v>
+        <v>281</v>
       </c>
       <c r="B165" s="2" t="s">
-        <v>323</v>
+        <v>269</v>
       </c>
       <c r="C165" s="2" t="s">
-        <v>325</v>
+        <v>271</v>
       </c>
       <c r="D165">
         <v>16</v>
@@ -4245,13 +4281,13 @@
     </row>
     <row r="166" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A166" s="2" t="s">
-        <v>336</v>
+        <v>282</v>
       </c>
       <c r="B166" s="2" t="s">
-        <v>324</v>
+        <v>270</v>
       </c>
       <c r="C166" s="2" t="s">
-        <v>325</v>
+        <v>271</v>
       </c>
       <c r="D166">
         <v>17</v>
@@ -4262,13 +4298,13 @@
     </row>
     <row r="167" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A167" s="2" t="s">
-        <v>341</v>
+        <v>287</v>
       </c>
       <c r="B167" s="2" t="s">
-        <v>337</v>
+        <v>283</v>
       </c>
       <c r="C167" s="2" t="s">
-        <v>340</v>
+        <v>286</v>
       </c>
       <c r="D167">
         <v>17</v>
@@ -4279,13 +4315,13 @@
     </row>
     <row r="168" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A168" s="2" t="s">
-        <v>342</v>
+        <v>288</v>
       </c>
       <c r="B168" s="2" t="s">
-        <v>338</v>
+        <v>284</v>
       </c>
       <c r="C168" s="2" t="s">
-        <v>340</v>
+        <v>286</v>
       </c>
       <c r="D168">
         <v>17</v>
@@ -4296,18 +4332,137 @@
     </row>
     <row r="169" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A169" s="2" t="s">
-        <v>343</v>
+        <v>289</v>
       </c>
       <c r="B169" s="2" t="s">
-        <v>339</v>
+        <v>285</v>
       </c>
       <c r="C169" s="2" t="s">
-        <v>340</v>
+        <v>286</v>
       </c>
       <c r="D169">
         <v>17</v>
       </c>
       <c r="E169">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="170" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A170" s="3" t="s">
+        <v>349</v>
+      </c>
+      <c r="B170" t="s">
+        <v>348</v>
+      </c>
+      <c r="C170" t="s">
+        <v>347</v>
+      </c>
+      <c r="D170">
+        <v>0</v>
+      </c>
+      <c r="E170">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="171" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A171" s="3" t="s">
+        <v>350</v>
+      </c>
+      <c r="B171" t="s">
+        <v>341</v>
+      </c>
+      <c r="C171" t="s">
+        <v>347</v>
+      </c>
+      <c r="D171">
+        <v>0</v>
+      </c>
+      <c r="E171">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="172" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A172" s="3" t="s">
+        <v>351</v>
+      </c>
+      <c r="B172" t="s">
+        <v>342</v>
+      </c>
+      <c r="C172" t="s">
+        <v>347</v>
+      </c>
+      <c r="D172">
+        <v>0</v>
+      </c>
+      <c r="E172">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="173" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A173" s="3" t="s">
+        <v>352</v>
+      </c>
+      <c r="B173" t="s">
+        <v>343</v>
+      </c>
+      <c r="C173" t="s">
+        <v>347</v>
+      </c>
+      <c r="D173">
+        <v>0</v>
+      </c>
+      <c r="E173">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="174" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A174" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="B174" t="s">
+        <v>344</v>
+      </c>
+      <c r="C174" t="s">
+        <v>347</v>
+      </c>
+      <c r="D174">
+        <v>0</v>
+      </c>
+      <c r="E174">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="175" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A175" s="3" t="s">
+        <v>354</v>
+      </c>
+      <c r="B175" t="s">
+        <v>345</v>
+      </c>
+      <c r="C175" t="s">
+        <v>347</v>
+      </c>
+      <c r="D175">
+        <v>0</v>
+      </c>
+      <c r="E175">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="176" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A176" s="3" t="s">
+        <v>355</v>
+      </c>
+      <c r="B176" t="s">
+        <v>346</v>
+      </c>
+      <c r="C176" t="s">
+        <v>347</v>
+      </c>
+      <c r="D176">
+        <v>0</v>
+      </c>
+      <c r="E176">
         <v>0</v>
       </c>
     </row>
